--- a/data/DCH/160kW_2dias/elmo_data.xlsx
+++ b/data/DCH/160kW_2dias/elmo_data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF138F13-80F0-49FB-9229-78A3AFC661D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
